--- a/data/processed/merged_ibm.xlsx
+++ b/data/processed/merged_ibm.xlsx
@@ -10114,7 +10114,7 @@
         <v>1.52</v>
       </c>
       <c r="G333" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="334">
@@ -10213,7 +10213,7 @@
         <v>3.69</v>
       </c>
       <c r="G336" t="n">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="337">
@@ -10576,7 +10576,7 @@
         <v>4.47</v>
       </c>
       <c r="G347" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
     </row>
     <row r="348">
@@ -10675,7 +10675,7 @@
         <v>601.73</v>
       </c>
       <c r="G350" t="n">
-        <v>581.72</v>
+        <v>581.73</v>
       </c>
     </row>
     <row r="351">
@@ -10741,7 +10741,7 @@
         <v>18.68</v>
       </c>
       <c r="G352" t="n">
-        <v>16.56</v>
+        <v>16.57</v>
       </c>
     </row>
     <row r="353">
@@ -10840,7 +10840,7 @@
         <v>80.05</v>
       </c>
       <c r="G355" t="n">
-        <v>38.68</v>
+        <v>38.72</v>
       </c>
     </row>
     <row r="356">
@@ -10870,10 +10870,10 @@
         </is>
       </c>
       <c r="F356" t="n">
-        <v>48.05</v>
+        <v>72.05</v>
       </c>
       <c r="G356" t="n">
-        <v>8.789999999999999</v>
+        <v>9.65</v>
       </c>
     </row>
     <row r="357">
@@ -11533,7 +11533,7 @@
         <v>1.31</v>
       </c>
       <c r="G376" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="377">
@@ -11995,7 +11995,7 @@
         <v>1.24</v>
       </c>
       <c r="G390" t="n">
-        <v>0.46</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="391">
@@ -12350,7 +12350,7 @@
         <v>0.27</v>
       </c>
       <c r="G401" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="402">
@@ -24819,7 +24819,7 @@
         <v>2.43</v>
       </c>
       <c r="G830" t="n">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
     </row>
     <row r="831">
@@ -24885,7 +24885,7 @@
         <v>634.95</v>
       </c>
       <c r="G832" t="n">
-        <v>380.44</v>
+        <v>383.25</v>
       </c>
     </row>
     <row r="833">
@@ -24918,7 +24918,7 @@
         <v>662.95</v>
       </c>
       <c r="G833" t="n">
-        <v>536.6</v>
+        <v>605.8200000000001</v>
       </c>
     </row>
     <row r="834">
@@ -24951,7 +24951,7 @@
         <v>23.32</v>
       </c>
       <c r="G834" t="n">
-        <v>15.06</v>
+        <v>19.49</v>
       </c>
     </row>
     <row r="835">
@@ -25182,7 +25182,7 @@
         <v>18.65</v>
       </c>
       <c r="G841" t="n">
-        <v>16.63</v>
+        <v>16.66</v>
       </c>
     </row>
     <row r="842">
@@ -25248,7 +25248,7 @@
         <v>42.05</v>
       </c>
       <c r="G843" t="n">
-        <v>16.2</v>
+        <v>16.21</v>
       </c>
     </row>
     <row r="844">
@@ -25278,10 +25278,10 @@
         </is>
       </c>
       <c r="F844" t="n">
-        <v>30.05</v>
+        <v>54.05</v>
       </c>
       <c r="G844" t="n">
-        <v>8.08</v>
+        <v>8.880000000000001</v>
       </c>
     </row>
     <row r="845">
@@ -25380,7 +25380,7 @@
         <v>0.47</v>
       </c>
       <c r="G847" t="n">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="848">
@@ -26618,7 +26618,7 @@
         <v>2.33</v>
       </c>
       <c r="G885" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
     </row>
     <row r="886">
